--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -585,7 +585,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DentAI — Security Findings Report</t>
+          <t>DentAI â€” Security Findings Report</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>No ownership check — any integer ID accepted</t>
+          <t>No ownership check â€” any integer ID accepted</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>File type checked by extension only — no MIME inspection</t>
+          <t>File type checked by extension only â€” no MIME inspection</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1848,7 +1848,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DentAI — API Endpoint Inventory</t>
+          <t>DentAI â€” API Endpoint Inventory</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DentAI — Risk Summary Dashboard</t>
+          <t>DentAI â€” Risk Summary Dashboard</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Immediate — before any deployment</t>
+          <t>Immediate â€” before any deployment</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
